--- a/aReport_card/2025_2026/Third_term/JSS2/Third_term_JSS2_Business_Studies.xlsx
+++ b/aReport_card/2025_2026/Third_term/JSS2/Third_term_JSS2_Business_Studies.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47C6977-75BF-467E-B94F-17B3BC47D23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56AE0AF8-104C-4BBD-9E2A-267CD35F4B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
   <si>
     <t>Admission_no</t>
   </si>
@@ -41,6 +41,9 @@
     <t>ABDUL-RAHAMAN</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>24002</t>
   </si>
   <si>
@@ -53,19 +56,22 @@
     <t>ILYAS</t>
   </si>
   <si>
+    <t>24005</t>
+  </si>
+  <si>
+    <t>QOZEEM</t>
+  </si>
+  <si>
     <t>24004</t>
   </si>
   <si>
     <t>SALAHUDEEN</t>
   </si>
   <si>
-    <t>24005</t>
+    <t>24006</t>
   </si>
   <si>
     <t>TEST</t>
-  </si>
-  <si>
-    <t>24006</t>
   </si>
   <si>
     <t>24007</t>
@@ -78,17 +84,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -114,9 +113,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -491,157 +489,165 @@
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1">
-        <v>34</v>
-      </c>
-      <c r="D2" s="1">
-        <v>28</v>
-      </c>
-      <c r="E2" s="1">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1">
-        <v>77</v>
+      <c r="C2">
+        <v>33</v>
+      </c>
+      <c r="D2">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <f t="shared" ref="F2:F9" si="0">SUM(C2:E2)</f>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1">
-        <v>33</v>
-      </c>
-      <c r="D3" s="1">
-        <v>28</v>
-      </c>
-      <c r="E3" s="1">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1">
-        <v>76</v>
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>36</v>
+      </c>
+      <c r="D3">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1">
-        <v>33</v>
-      </c>
-      <c r="D4" s="1">
-        <v>28</v>
-      </c>
-      <c r="E4" s="1">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1">
-        <v>76</v>
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>34</v>
+      </c>
+      <c r="D4">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1">
-        <v>33</v>
-      </c>
-      <c r="D5" s="1">
-        <v>28</v>
-      </c>
-      <c r="E5" s="1">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1">
-        <v>76</v>
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>31</v>
+      </c>
+      <c r="D5">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="1">
-        <v>33</v>
-      </c>
-      <c r="D6" s="1">
-        <v>28</v>
-      </c>
-      <c r="E6" s="1">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1">
-        <v>76</v>
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>32</v>
+      </c>
+      <c r="D6">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="1">
-        <v>33</v>
-      </c>
-      <c r="D7" s="1">
-        <v>28</v>
-      </c>
-      <c r="E7" s="1">
-        <v>15</v>
-      </c>
-      <c r="F7" s="1">
-        <v>76</v>
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1">
-        <v>34</v>
-      </c>
-      <c r="D8" s="1">
-        <v>28</v>
-      </c>
-      <c r="E8" s="1">
-        <v>15</v>
-      </c>
-      <c r="F8" s="1">
-        <v>77</v>
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="1">
-        <v>29</v>
-      </c>
-      <c r="D9" s="1">
-        <v>28</v>
-      </c>
-      <c r="E9" s="1">
-        <v>15</v>
-      </c>
-      <c r="F9" s="1">
-        <v>72</v>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
